--- a/deliverables/PBCP-BH-03_rev4.xlsx
+++ b/deliverables/PBCP-BH-03_rev4.xlsx
@@ -12727,13 +12727,15 @@
         <v>39</v>
       </c>
       <c r="C14" s="8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>40</v>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GWL analisis likuefaksi (Report BP-00-GEO-RPT-003)</t>
+        </is>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
@@ -12765,13 +12767,15 @@
         <v>45</v>
       </c>
       <c r="C16" s="8">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E16" s="7" t="s">
-        <v>47</v>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Report Tabel 5.1</t>
+        </is>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
@@ -12782,13 +12786,15 @@
         <v>49</v>
       </c>
       <c r="C17" s="8">
-        <v>18.399999999999999</v>
+        <v>19.0</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>47</v>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Report Tabel 5.1</t>
+        </is>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
@@ -12943,8 +12949,10 @@
       <c r="D26" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E26" s="7" t="s">
-        <v>70</v>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sesuai perhitungan sebelumnya</t>
+        </is>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -12958,8 +12966,10 @@
       <c r="D27" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E27" s="7" t="s">
-        <v>70</v>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sesuai perhitungan sebelumnya</t>
+        </is>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -13199,7 +13209,11 @@
       <c r="D45" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E45" s="7"/>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DD_max tidak difaktorkan (beban faktor 1,0)</t>
+        </is>
+      </c>
     </row>
     <row r="47" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
@@ -13223,7 +13237,11 @@
       <c r="D48" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E48" s="7"/>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beban uji pengguna - Logyard belum ada hasil GROUP</t>
+        </is>
+      </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
@@ -13468,8 +13486,10 @@
       <c r="G7" s="11">
         <v>0</v>
       </c>
-      <c r="H7" s="6" t="s">
-        <v>128</v>
+      <c r="H7" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I7" s="16">
         <f>IF(F7="Clay",Input!$C$32*G7,0)</f>
@@ -13511,14 +13531,18 @@
       <c r="E8" s="19">
         <f t="shared" si="1"/>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>127</v>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand</t>
+        </is>
       </c>
       <c r="G8" s="11">
-        <v>50</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>128</v>
+        <v>10</v>
+      </c>
+      <c r="H8" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I8" s="20">
         <f>IF(F8="Clay",Input!$C$32*G8,0)</f>
@@ -13539,7 +13563,9 @@
         <f>IF(F8="Clay",Input!$C$35*I8,MIN(Input!$C$33*G8,Input!$C$34)/9.81)</f>
       </c>
       <c r="O8" s="21"/>
-      <c r="P8" s="11"/>
+      <c r="P8" s="11">
+        <v>0.43</v>
+      </c>
       <c r="Q8" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B8),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
       </c>
@@ -13560,14 +13586,18 @@
       <c r="E9" s="9">
         <f t="shared" si="1"/>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>127</v>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand</t>
+        </is>
       </c>
       <c r="G9" s="11">
-        <v>50</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>128</v>
+        <v>18</v>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I9" s="16">
         <f>IF(F9="Clay",Input!$C$32*G9,0)</f>
@@ -13588,7 +13618,9 @@
         <f>IF(F9="Clay",Input!$C$35*I9,MIN(Input!$C$33*G9,Input!$C$34)/9.81)</f>
       </c>
       <c r="O9" s="17"/>
-      <c r="P9" s="11"/>
+      <c r="P9" s="11">
+        <v>0.26</v>
+      </c>
       <c r="Q9" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B9),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
       </c>
@@ -13609,14 +13641,18 @@
       <c r="E10" s="19">
         <f t="shared" si="1"/>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>127</v>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand</t>
+        </is>
       </c>
       <c r="G10" s="11">
-        <v>41</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>128</v>
+        <v>13</v>
+      </c>
+      <c r="H10" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I10" s="20">
         <f>IF(F10="Clay",Input!$C$32*G10,0)</f>
@@ -13638,7 +13674,7 @@
       </c>
       <c r="O10" s="21"/>
       <c r="P10" s="11">
-        <v>0.21</v>
+        <v>0.43</v>
       </c>
       <c r="Q10" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B10),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -13660,14 +13696,18 @@
       <c r="E11" s="9">
         <f t="shared" si="1"/>
       </c>
-      <c r="F11" s="6" t="s">
-        <v>127</v>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clay</t>
+        </is>
       </c>
       <c r="G11" s="11">
-        <v>50</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>128</v>
+        <v>8</v>
+      </c>
+      <c r="H11" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I11" s="16">
         <f>IF(F11="Clay",Input!$C$32*G11,0)</f>
@@ -13688,7 +13728,9 @@
         <f>IF(F11="Clay",Input!$C$35*I11,MIN(Input!$C$33*G11,Input!$C$34)/9.81)</f>
       </c>
       <c r="O11" s="17"/>
-      <c r="P11" s="11"/>
+      <c r="P11" s="11">
+        <v>0.56</v>
+      </c>
       <c r="Q11" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B11),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
       </c>
@@ -13709,14 +13751,18 @@
       <c r="E12" s="19">
         <f t="shared" si="1"/>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>127</v>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand</t>
+        </is>
       </c>
       <c r="G12" s="11">
-        <v>26</v>
-      </c>
-      <c r="H12" s="22" t="s">
-        <v>129</v>
+        <v>10</v>
+      </c>
+      <c r="H12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I12" s="20">
         <f>IF(F12="Clay",Input!$C$32*G12,0)</f>
@@ -13738,7 +13784,7 @@
       </c>
       <c r="O12" s="21"/>
       <c r="P12" s="11">
-        <v>2.68</v>
+        <v>0.56</v>
       </c>
       <c r="Q12" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B12),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -13760,14 +13806,18 @@
       <c r="E13" s="9">
         <f t="shared" si="1"/>
       </c>
-      <c r="F13" s="6" t="s">
-        <v>127</v>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand</t>
+        </is>
       </c>
       <c r="G13" s="11">
-        <v>15</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>129</v>
+        <v>29</v>
+      </c>
+      <c r="H13" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I13" s="16">
         <f>IF(F13="Clay",Input!$C$32*G13,0)</f>
@@ -13789,7 +13839,7 @@
       </c>
       <c r="O13" s="17"/>
       <c r="P13" s="11">
-        <v>3.45</v>
+        <v>0.53</v>
       </c>
       <c r="Q13" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B13),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -13811,14 +13861,18 @@
       <c r="E14" s="19">
         <f t="shared" si="1"/>
       </c>
-      <c r="F14" s="6" t="s">
-        <v>127</v>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clay</t>
+        </is>
       </c>
       <c r="G14" s="11">
-        <v>25</v>
-      </c>
-      <c r="H14" s="22" t="s">
-        <v>129</v>
+        <v>24</v>
+      </c>
+      <c r="H14" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L</t>
+        </is>
       </c>
       <c r="I14" s="20">
         <f>IF(F14="Clay",Input!$C$32*G14,0)</f>
@@ -13862,14 +13916,18 @@
       <c r="E15" s="9">
         <f t="shared" si="1"/>
       </c>
-      <c r="F15" s="6" t="s">
-        <v>130</v>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clay</t>
+        </is>
       </c>
       <c r="G15" s="11">
-        <v>20</v>
-      </c>
-      <c r="H15" s="22" t="s">
-        <v>129</v>
+        <v>10</v>
+      </c>
+      <c r="H15" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L</t>
+        </is>
       </c>
       <c r="I15" s="16">
         <f>IF(F15="Clay",Input!$C$32*G15,0)</f>
@@ -13891,7 +13949,7 @@
       </c>
       <c r="O15" s="17"/>
       <c r="P15" s="11">
-        <v>3.45</v>
+        <v>4.44</v>
       </c>
       <c r="Q15" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B15),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -13913,14 +13971,18 @@
       <c r="E16" s="19">
         <f t="shared" si="1"/>
       </c>
-      <c r="F16" s="6" t="s">
-        <v>130</v>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand</t>
+        </is>
       </c>
       <c r="G16" s="11">
-        <v>47</v>
-      </c>
-      <c r="H16" s="22" t="s">
-        <v>129</v>
+        <v>35</v>
+      </c>
+      <c r="H16" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L</t>
+        </is>
       </c>
       <c r="I16" s="20">
         <f>IF(F16="Clay",Input!$C$32*G16,0)</f>
@@ -13942,7 +14004,7 @@
       </c>
       <c r="O16" s="21"/>
       <c r="P16" s="11">
-        <v>0.16</v>
+        <v>1.31</v>
       </c>
       <c r="Q16" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B16),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -13964,14 +14026,18 @@
       <c r="E17" s="9">
         <f t="shared" si="1"/>
       </c>
-      <c r="F17" s="6" t="s">
-        <v>127</v>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand</t>
+        </is>
       </c>
       <c r="G17" s="11">
-        <v>12</v>
-      </c>
-      <c r="H17" s="22" t="s">
-        <v>129</v>
+        <v>39</v>
+      </c>
+      <c r="H17" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I17" s="16">
         <f>IF(F17="Clay",Input!$C$32*G17,0)</f>
@@ -13993,7 +14059,7 @@
       </c>
       <c r="O17" s="17"/>
       <c r="P17" s="11">
-        <v>4.44</v>
+        <v>0.21</v>
       </c>
       <c r="Q17" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B17),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14015,14 +14081,18 @@
       <c r="E18" s="19">
         <f t="shared" si="1"/>
       </c>
-      <c r="F18" s="6" t="s">
-        <v>127</v>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand</t>
+        </is>
       </c>
       <c r="G18" s="11">
-        <v>23</v>
-      </c>
-      <c r="H18" s="22" t="s">
-        <v>129</v>
+        <v>26</v>
+      </c>
+      <c r="H18" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L</t>
+        </is>
       </c>
       <c r="I18" s="20">
         <f>IF(F18="Clay",Input!$C$32*G18,0)</f>
@@ -14044,7 +14114,7 @@
       </c>
       <c r="O18" s="21"/>
       <c r="P18" s="11">
-        <v>3.45</v>
+        <v>2.68</v>
       </c>
       <c r="Q18" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B18),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14066,14 +14136,18 @@
       <c r="E19" s="9">
         <f t="shared" si="1"/>
       </c>
-      <c r="F19" s="6" t="s">
-        <v>127</v>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand</t>
+        </is>
       </c>
       <c r="G19" s="11">
-        <v>30</v>
-      </c>
-      <c r="H19" s="22" t="s">
-        <v>129</v>
+        <v>22</v>
+      </c>
+      <c r="H19" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I19" s="16">
         <f>IF(F19="Clay",Input!$C$32*G19,0)</f>
@@ -14095,7 +14169,7 @@
       </c>
       <c r="O19" s="17"/>
       <c r="P19" s="11">
-        <v>2.68</v>
+        <v>0.43</v>
       </c>
       <c r="Q19" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B19),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14117,14 +14191,18 @@
       <c r="E20" s="19">
         <f t="shared" si="1"/>
       </c>
-      <c r="F20" s="6" t="s">
-        <v>127</v>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sand</t>
+        </is>
       </c>
       <c r="G20" s="11">
-        <v>27</v>
-      </c>
-      <c r="H20" s="22" t="s">
-        <v>129</v>
+        <v>24</v>
+      </c>
+      <c r="H20" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">L</t>
+        </is>
       </c>
       <c r="I20" s="20">
         <f>IF(F20="Clay",Input!$C$32*G20,0)</f>
@@ -14146,7 +14224,7 @@
       </c>
       <c r="O20" s="21"/>
       <c r="P20" s="11">
-        <v>2.68</v>
+        <v>3.45</v>
       </c>
       <c r="Q20" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B20),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14168,14 +14246,18 @@
       <c r="E21" s="9">
         <f t="shared" si="1"/>
       </c>
-      <c r="F21" s="6" t="s">
-        <v>127</v>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clay</t>
+        </is>
       </c>
       <c r="G21" s="11">
-        <v>28</v>
-      </c>
-      <c r="H21" s="6" t="s">
-        <v>128</v>
+        <v>38</v>
+      </c>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I21" s="16">
         <f>IF(F21="Clay",Input!$C$32*G21,0)</f>
@@ -14197,7 +14279,7 @@
       </c>
       <c r="O21" s="17"/>
       <c r="P21" s="11">
-        <v>2.68</v>
+        <v>0.26</v>
       </c>
       <c r="Q21" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B21),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14225,8 +14307,10 @@
       <c r="G22" s="11">
         <v>24</v>
       </c>
-      <c r="H22" s="6" t="s">
-        <v>128</v>
+      <c r="H22" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I22" s="20">
         <f>IF(F22="Clay",Input!$C$32*G22,0)</f>
@@ -14246,7 +14330,11 @@
       <c r="N22" s="20">
         <f>IF(F22="Clay",Input!$C$35*I22,MIN(Input!$C$33*G22,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O22" s="21"/>
+      <c r="O22" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P22" s="11"/>
       <c r="Q22" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B22),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14274,8 +14362,10 @@
       <c r="G23" s="11">
         <v>44</v>
       </c>
-      <c r="H23" s="6" t="s">
-        <v>128</v>
+      <c r="H23" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I23" s="16">
         <f>IF(F23="Clay",Input!$C$32*G23,0)</f>
@@ -14295,7 +14385,11 @@
       <c r="N23" s="16">
         <f>IF(F23="Clay",Input!$C$35*I23,MIN(Input!$C$33*G23,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O23" s="17"/>
+      <c r="O23" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P23" s="11"/>
       <c r="Q23" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B23),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14323,8 +14417,10 @@
       <c r="G24" s="11">
         <v>21</v>
       </c>
-      <c r="H24" s="6" t="s">
-        <v>128</v>
+      <c r="H24" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I24" s="20">
         <f>IF(F24="Clay",Input!$C$32*G24,0)</f>
@@ -14344,7 +14440,11 @@
       <c r="N24" s="20">
         <f>IF(F24="Clay",Input!$C$35*I24,MIN(Input!$C$33*G24,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O24" s="21"/>
+      <c r="O24" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P24" s="11"/>
       <c r="Q24" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B24),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14372,8 +14472,10 @@
       <c r="G25" s="11">
         <v>31</v>
       </c>
-      <c r="H25" s="6" t="s">
-        <v>128</v>
+      <c r="H25" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I25" s="16">
         <f>IF(F25="Clay",Input!$C$32*G25,0)</f>
@@ -14393,7 +14495,11 @@
       <c r="N25" s="16">
         <f>IF(F25="Clay",Input!$C$35*I25,MIN(Input!$C$33*G25,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O25" s="17"/>
+      <c r="O25" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P25" s="11"/>
       <c r="Q25" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B25),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14421,8 +14527,10 @@
       <c r="G26" s="11">
         <v>50</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>128</v>
+      <c r="H26" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I26" s="20">
         <f>IF(F26="Clay",Input!$C$32*G26,0)</f>
@@ -14442,7 +14550,11 @@
       <c r="N26" s="20">
         <f>IF(F26="Clay",Input!$C$35*I26,MIN(Input!$C$33*G26,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O26" s="21"/>
+      <c r="O26" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P26" s="11"/>
       <c r="Q26" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B26),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14470,8 +14582,10 @@
       <c r="G27" s="11">
         <v>40</v>
       </c>
-      <c r="H27" s="6" t="s">
-        <v>128</v>
+      <c r="H27" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I27" s="16">
         <f>IF(F27="Clay",Input!$C$32*G27,0)</f>
@@ -14491,7 +14605,11 @@
       <c r="N27" s="16">
         <f>IF(F27="Clay",Input!$C$35*I27,MIN(Input!$C$33*G27,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O27" s="17"/>
+      <c r="O27" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P27" s="11"/>
       <c r="Q27" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B27),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14519,8 +14637,10 @@
       <c r="G28" s="11">
         <v>43</v>
       </c>
-      <c r="H28" s="6" t="s">
-        <v>128</v>
+      <c r="H28" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I28" s="20">
         <f>IF(F28="Clay",Input!$C$32*G28,0)</f>
@@ -14540,7 +14660,11 @@
       <c r="N28" s="20">
         <f>IF(F28="Clay",Input!$C$35*I28,MIN(Input!$C$33*G28,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O28" s="21"/>
+      <c r="O28" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P28" s="11"/>
       <c r="Q28" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B28),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14568,8 +14692,10 @@
       <c r="G29" s="11">
         <v>26</v>
       </c>
-      <c r="H29" s="6" t="s">
-        <v>128</v>
+      <c r="H29" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I29" s="16">
         <f>IF(F29="Clay",Input!$C$32*G29,0)</f>
@@ -14589,7 +14715,11 @@
       <c r="N29" s="16">
         <f>IF(F29="Clay",Input!$C$35*I29,MIN(Input!$C$33*G29,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O29" s="17"/>
+      <c r="O29" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P29" s="11"/>
       <c r="Q29" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B29),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14617,8 +14747,10 @@
       <c r="G30" s="11">
         <v>53</v>
       </c>
-      <c r="H30" s="6" t="s">
-        <v>128</v>
+      <c r="H30" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I30" s="20">
         <f>IF(F30="Clay",Input!$C$32*G30,0)</f>
@@ -14638,7 +14770,11 @@
       <c r="N30" s="20">
         <f>IF(F30="Clay",Input!$C$35*I30,MIN(Input!$C$33*G30,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O30" s="21"/>
+      <c r="O30" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P30" s="11"/>
       <c r="Q30" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B30),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14666,8 +14802,10 @@
       <c r="G31" s="11">
         <v>54</v>
       </c>
-      <c r="H31" s="6" t="s">
-        <v>128</v>
+      <c r="H31" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I31" s="16">
         <f>IF(F31="Clay",Input!$C$32*G31,0)</f>
@@ -14687,7 +14825,11 @@
       <c r="N31" s="16">
         <f>IF(F31="Clay",Input!$C$35*I31,MIN(Input!$C$33*G31,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O31" s="17"/>
+      <c r="O31" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P31" s="11"/>
       <c r="Q31" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B31),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14715,8 +14857,10 @@
       <c r="G32" s="11">
         <v>50</v>
       </c>
-      <c r="H32" s="6" t="s">
-        <v>128</v>
+      <c r="H32" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I32" s="20">
         <f>IF(F32="Clay",Input!$C$32*G32,0)</f>
@@ -14736,7 +14880,11 @@
       <c r="N32" s="20">
         <f>IF(F32="Clay",Input!$C$35*I32,MIN(Input!$C$33*G32,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O32" s="21"/>
+      <c r="O32" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P32" s="11"/>
       <c r="Q32" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B32),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14764,8 +14912,10 @@
       <c r="G33" s="11">
         <v>50</v>
       </c>
-      <c r="H33" s="6" t="s">
-        <v>128</v>
+      <c r="H33" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I33" s="16">
         <f>IF(F33="Clay",Input!$C$32*G33,0)</f>
@@ -14785,7 +14935,11 @@
       <c r="N33" s="16">
         <f>IF(F33="Clay",Input!$C$35*I33,MIN(Input!$C$33*G33,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O33" s="17"/>
+      <c r="O33" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P33" s="11"/>
       <c r="Q33" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B33),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14813,8 +14967,10 @@
       <c r="G34" s="11">
         <v>37</v>
       </c>
-      <c r="H34" s="6" t="s">
-        <v>128</v>
+      <c r="H34" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I34" s="20">
         <f>IF(F34="Clay",Input!$C$32*G34,0)</f>
@@ -14834,7 +14990,11 @@
       <c r="N34" s="20">
         <f>IF(F34="Clay",Input!$C$35*I34,MIN(Input!$C$33*G34,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O34" s="21"/>
+      <c r="O34" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P34" s="11"/>
       <c r="Q34" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B34),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14862,8 +15022,10 @@
       <c r="G35" s="11">
         <v>50</v>
       </c>
-      <c r="H35" s="6" t="s">
-        <v>128</v>
+      <c r="H35" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I35" s="16">
         <f>IF(F35="Clay",Input!$C$32*G35,0)</f>
@@ -14883,7 +15045,11 @@
       <c r="N35" s="16">
         <f>IF(F35="Clay",Input!$C$35*I35,MIN(Input!$C$33*G35,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O35" s="17"/>
+      <c r="O35" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P35" s="11"/>
       <c r="Q35" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B35),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14911,8 +15077,10 @@
       <c r="G36" s="11">
         <v>50</v>
       </c>
-      <c r="H36" s="6" t="s">
-        <v>128</v>
+      <c r="H36" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I36" s="20">
         <f>IF(F36="Clay",Input!$C$32*G36,0)</f>
@@ -14932,7 +15100,11 @@
       <c r="N36" s="20">
         <f>IF(F36="Clay",Input!$C$35*I36,MIN(Input!$C$33*G36,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O36" s="21"/>
+      <c r="O36" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P36" s="11"/>
       <c r="Q36" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B36),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -14960,8 +15132,10 @@
       <c r="G37" s="11">
         <v>50</v>
       </c>
-      <c r="H37" s="6" t="s">
-        <v>128</v>
+      <c r="H37" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I37" s="16">
         <f>IF(F37="Clay",Input!$C$32*G37,0)</f>
@@ -14981,7 +15155,11 @@
       <c r="N37" s="16">
         <f>IF(F37="Clay",Input!$C$35*I37,MIN(Input!$C$33*G37,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O37" s="17"/>
+      <c r="O37" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P37" s="11"/>
       <c r="Q37" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B37),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15009,8 +15187,10 @@
       <c r="G38" s="11">
         <v>50</v>
       </c>
-      <c r="H38" s="6" t="s">
-        <v>128</v>
+      <c r="H38" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I38" s="20">
         <f>IF(F38="Clay",Input!$C$32*G38,0)</f>
@@ -15030,7 +15210,11 @@
       <c r="N38" s="20">
         <f>IF(F38="Clay",Input!$C$35*I38,MIN(Input!$C$33*G38,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O38" s="21"/>
+      <c r="O38" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P38" s="11"/>
       <c r="Q38" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B38),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15058,8 +15242,10 @@
       <c r="G39" s="11">
         <v>27</v>
       </c>
-      <c r="H39" s="6" t="s">
-        <v>128</v>
+      <c r="H39" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I39" s="16">
         <f>IF(F39="Clay",Input!$C$32*G39,0)</f>
@@ -15079,7 +15265,11 @@
       <c r="N39" s="16">
         <f>IF(F39="Clay",Input!$C$35*I39,MIN(Input!$C$33*G39,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O39" s="17"/>
+      <c r="O39" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P39" s="11"/>
       <c r="Q39" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B39),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15107,8 +15297,10 @@
       <c r="G40" s="11">
         <v>25</v>
       </c>
-      <c r="H40" s="6" t="s">
-        <v>128</v>
+      <c r="H40" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I40" s="20">
         <f>IF(F40="Clay",Input!$C$32*G40,0)</f>
@@ -15128,7 +15320,11 @@
       <c r="N40" s="20">
         <f>IF(F40="Clay",Input!$C$35*I40,MIN(Input!$C$33*G40,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O40" s="21"/>
+      <c r="O40" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P40" s="11"/>
       <c r="Q40" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B40),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15156,8 +15352,10 @@
       <c r="G41" s="11">
         <v>29</v>
       </c>
-      <c r="H41" s="6" t="s">
-        <v>128</v>
+      <c r="H41" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I41" s="16">
         <f>IF(F41="Clay",Input!$C$32*G41,0)</f>
@@ -15177,7 +15375,11 @@
       <c r="N41" s="16">
         <f>IF(F41="Clay",Input!$C$35*I41,MIN(Input!$C$33*G41,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O41" s="17"/>
+      <c r="O41" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P41" s="11"/>
       <c r="Q41" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B41),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15205,8 +15407,10 @@
       <c r="G42" s="11">
         <v>35</v>
       </c>
-      <c r="H42" s="6" t="s">
-        <v>128</v>
+      <c r="H42" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I42" s="20">
         <f>IF(F42="Clay",Input!$C$32*G42,0)</f>
@@ -15226,7 +15430,11 @@
       <c r="N42" s="20">
         <f>IF(F42="Clay",Input!$C$35*I42,MIN(Input!$C$33*G42,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O42" s="21"/>
+      <c r="O42" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P42" s="11"/>
       <c r="Q42" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B42),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15254,8 +15462,10 @@
       <c r="G43" s="11">
         <v>50</v>
       </c>
-      <c r="H43" s="6" t="s">
-        <v>128</v>
+      <c r="H43" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I43" s="16">
         <f>IF(F43="Clay",Input!$C$32*G43,0)</f>
@@ -15275,7 +15485,11 @@
       <c r="N43" s="16">
         <f>IF(F43="Clay",Input!$C$35*I43,MIN(Input!$C$33*G43,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O43" s="17"/>
+      <c r="O43" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P43" s="11"/>
       <c r="Q43" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B43),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15303,8 +15517,10 @@
       <c r="G44" s="11">
         <v>50</v>
       </c>
-      <c r="H44" s="6" t="s">
-        <v>128</v>
+      <c r="H44" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I44" s="20">
         <f>IF(F44="Clay",Input!$C$32*G44,0)</f>
@@ -15324,7 +15540,11 @@
       <c r="N44" s="20">
         <f>IF(F44="Clay",Input!$C$35*I44,MIN(Input!$C$33*G44,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O44" s="21"/>
+      <c r="O44" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P44" s="11"/>
       <c r="Q44" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B44),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15352,8 +15572,10 @@
       <c r="G45" s="11">
         <v>50</v>
       </c>
-      <c r="H45" s="6" t="s">
-        <v>128</v>
+      <c r="H45" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I45" s="16">
         <f>IF(F45="Clay",Input!$C$32*G45,0)</f>
@@ -15373,7 +15595,11 @@
       <c r="N45" s="16">
         <f>IF(F45="Clay",Input!$C$35*I45,MIN(Input!$C$33*G45,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O45" s="17"/>
+      <c r="O45" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P45" s="11"/>
       <c r="Q45" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B45),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15401,8 +15627,10 @@
       <c r="G46" s="11">
         <v>29</v>
       </c>
-      <c r="H46" s="6" t="s">
-        <v>128</v>
+      <c r="H46" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I46" s="20">
         <f>IF(F46="Clay",Input!$C$32*G46,0)</f>
@@ -15422,7 +15650,11 @@
       <c r="N46" s="20">
         <f>IF(F46="Clay",Input!$C$35*I46,MIN(Input!$C$33*G46,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O46" s="21"/>
+      <c r="O46" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P46" s="11"/>
       <c r="Q46" s="20">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B46),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>
@@ -15450,8 +15682,10 @@
       <c r="G47" s="11">
         <v>44</v>
       </c>
-      <c r="H47" s="6" t="s">
-        <v>128</v>
+      <c r="H47" s="6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">NL</t>
+        </is>
       </c>
       <c r="I47" s="16">
         <f>IF(F47="Clay",Input!$C$32*G47,0)</f>
@@ -15471,7 +15705,11 @@
       <c r="N47" s="16">
         <f>IF(F47="Clay",Input!$C$35*I47,MIN(Input!$C$33*G47,Input!$C$34)/9.81)</f>
       </c>
-      <c r="O47" s="17"/>
+      <c r="O47" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Data salinan BH-02 (bor hanya s/d 22.5 m)</t>
+        </is>
+      </c>
       <c r="P47" s="11"/>
       <c r="Q47" s="16">
         <f>10*SUMPRODUCT(--($B$7:$B$47&gt;=B47),--($H$7:$H$47="L"),$D$7:$D$47,$P$7:$P$47+($P$7:$P$47="")*Input!$C$24)</f>

--- a/deliverables/PBCP-BH-03_rev4.xlsx
+++ b/deliverables/PBCP-BH-03_rev4.xlsx
@@ -13232,14 +13232,14 @@
         <v>9</v>
       </c>
       <c r="C48" s="14">
-        <v>3000</v>
+        <v>3000.0</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">beban uji pengguna - Logyard belum ada hasil GROUP</t>
+          <t xml:space="preserve">beban seragam semua BH (sama dengan BH-03) - update dgn GROUP beban revisi</t>
         </is>
       </c>
     </row>
@@ -13251,12 +13251,16 @@
         <v>13</v>
       </c>
       <c r="C49" s="14">
-        <v>600</v>
+        <v>600.0</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E49" s="7"/>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beban seragam semua BH (sama dengan BH-03) - update dgn GROUP beban revisi</t>
+        </is>
+      </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
@@ -13266,12 +13270,16 @@
         <v>18</v>
       </c>
       <c r="C50" s="14">
-        <v>500</v>
+        <v>500.0</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E50" s="7"/>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">beban seragam semua BH (sama dengan BH-03) - update dgn GROUP beban revisi</t>
+        </is>
+      </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
@@ -13281,12 +13289,16 @@
         <v>108</v>
       </c>
       <c r="C51" s="14">
-        <v>0</v>
+        <v>0.0</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E51" s="7"/>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">tidak ada tiang tarik pada kombinasi yang ditinjau</t>
+        </is>
+      </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
